--- a/SGC-CKN/Excel/994164ae-7868-4a32-8af2-201eaa43099d_Cáp_treo_-_Khu_VAP_TP-2_D1200_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/994164ae-7868-4a32-8af2-201eaa43099d_Cáp_treo_-_Khu_VAP_TP-2_D1200_14-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="81">
   <si>
     <t>Dự án</t>
   </si>
@@ -29,13 +29,13 @@
     <t>Tên bộ phận</t>
   </si>
   <si>
-    <t>Cáp treo - Khu VAP</t>
+    <t>Cáp treo - Khu VAP - Xã Cần Giờ, Thành phố Hồ Chí Minh</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TP-2</t>
+    <t>TP-02</t>
   </si>
   <si>
     <t>Biên bản số</t>
@@ -47,19 +47,19 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1200</t>
+    <t>1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>11:09 13/03/2026</t>
+    <t>11:00 13/03/2025</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>10:15 14/03/2026</t>
+    <t>10:15 14/03/2025</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,27 +99,27 @@
   </si>
   <si>
     <t xml:space="preserve">11:09
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">11:15
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">11:25
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">11:35
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">11:50
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">12:05
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t>2</t>
@@ -129,18 +129,15 @@
   </si>
   <si>
     <t xml:space="preserve">12:15
-13/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:00
-13/03/2026</t>
-  </si>
-  <si>
-    <t>Ghi nhận mâu thuẫn thời gian tại hiện trường (trùng lắp với lớp trước)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:18
-13/03/2026</t>
+13/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00
+13/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15
+13/03/2025</t>
   </si>
   <si>
     <t>3</t>
@@ -149,119 +146,120 @@
     <t>Sét pha màu xám ghi, xám vàng, trạng thái dẻo cứng đến nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">12:33
-13/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:45
-13/03/2026</t>
+    <t xml:space="preserve">17:18
+13/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:33
+13/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:45
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">20:29
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">20:40
-13/03/2026</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:59
-13/03/2026</t>
+13/03/2025</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát hạt mịn đến hạt vừa màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:50
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">21:10
-13/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:29
-13/03/2026</t>
+13/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:20
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">22:02
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">22:14
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">22:30
-13/03/2026</t>
+13/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">01:18
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">01:25
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">01:35
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">01:50
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">02:08
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">03:35
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">03:55
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">04:08
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">04:20
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">04:50
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">07:32
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">07:42
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">08:23
-14/03/2026</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát hạt mịn đến hạt vừa màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến chặt</t>
+14/03/2025</t>
   </si>
   <si>
     <t xml:space="preserve">08:45
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>Cát mịn đến vừa, màu xám nâu, xám ghi, đôi chỗ lẫn sạn, kết cấu rất chặt</t>
+    <t>Cát mịn đến vừa, màu xám nâu, xám ghi, đôi chỗ lẫn san, kết cấu rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:15
-14/03/2026</t>
+14/03/2025</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -289,9 +287,6 @@
   </si>
   <si>
     <t>V TB (m/h)</t>
-  </si>
-  <si>
-    <t>(Chưa có)</t>
   </si>
   <si>
     <t>TỔNG CỘNG</t>
@@ -301,7 +296,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -363,11 +358,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF365314"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -380,7 +370,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,11 +430,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
     <fill>
@@ -540,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -608,22 +593,13 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1416,7 +1392,7 @@
         <v>37</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" s="9">
         <v>-8.85</v>
@@ -1434,56 +1410,56 @@
         <v>8</v>
       </c>
       <c r="K17" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="9">
+      <c r="E18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="12">
         <v>-10.85</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="12">
         <v>-12.85</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="12">
         <v>0.05</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="12">
         <v>2</v>
       </c>
       <c r="J18" s="8">
         <v>40</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>41</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>39</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>42</v>
@@ -1509,13 +1485,13 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>42</v>
@@ -1544,13 +1520,13 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>43</v>
@@ -1565,13 +1541,13 @@
         <v>-18.85</v>
       </c>
       <c r="H21" s="12">
-        <v>7.73</v>
+        <v>2.73</v>
       </c>
       <c r="I21" s="12">
         <v>2</v>
       </c>
       <c r="J21" s="15">
-        <v>0.26</v>
+        <v>0.73</v>
       </c>
       <c r="K21" s="13" t="s">
         <v>9</v>
@@ -1579,13 +1555,13 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>44</v>
@@ -1620,13 +1596,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="16">
         <v>-20.85</v>
@@ -1635,13 +1611,13 @@
         <v>-22.85</v>
       </c>
       <c r="H23" s="16">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I23" s="16">
         <v>2</v>
       </c>
       <c r="J23" s="8">
-        <v>6.32</v>
+        <v>12</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>9</v>
@@ -1655,13 +1631,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" s="16">
         <v>-22.85</v>
@@ -1670,13 +1646,13 @@
         <v>-24.85</v>
       </c>
       <c r="H24" s="16">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="I24" s="16">
         <v>2</v>
       </c>
       <c r="J24" s="8">
-        <v>10.91</v>
+        <v>6</v>
       </c>
       <c r="K24" s="17" t="s">
         <v>9</v>
@@ -1690,13 +1666,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F25" s="16">
         <v>-24.85</v>
@@ -1705,13 +1681,13 @@
         <v>-26.85</v>
       </c>
       <c r="H25" s="16">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="I25" s="16">
         <v>2</v>
       </c>
       <c r="J25" s="8">
-        <v>6.32</v>
+        <v>12</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>9</v>
@@ -1725,13 +1701,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F26" s="16">
         <v>-26.85</v>
@@ -1760,13 +1736,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F27" s="16">
         <v>-28.85</v>
@@ -1795,13 +1771,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" s="16">
         <v>-30.85</v>
@@ -1830,13 +1806,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" s="16">
         <v>-32.85</v>
@@ -1865,13 +1841,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" s="16">
         <v>-34.85</v>
@@ -1900,13 +1876,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" s="16">
         <v>-36.85</v>
@@ -1935,13 +1911,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F32" s="16">
         <v>-38.85</v>
@@ -1970,13 +1946,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F33" s="16">
         <v>-40.85</v>
@@ -2005,13 +1981,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F34" s="16">
         <v>-42.85</v>
@@ -2040,13 +2016,13 @@
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F35" s="16">
         <v>-44.85</v>
@@ -2075,13 +2051,13 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F36" s="16">
         <v>-46.85</v>
@@ -2110,13 +2086,13 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F37" s="16">
         <v>-48.85</v>
@@ -2138,89 +2114,89 @@
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="21" t="s">
+      <c r="E38" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F38" s="20">
+      <c r="F38" s="16">
         <v>-50.05</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="16">
         <v>-53.05</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="16">
         <v>0.37</v>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="16">
         <v>3</v>
       </c>
       <c r="J38" s="8">
         <v>8.18</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="24" t="s">
+      <c r="D39" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" s="23">
+      <c r="F39" s="20">
         <v>-53.05</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="20">
         <v>-55.05</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="20">
         <v>1.5</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="20">
         <v>2</v>
       </c>
       <c r="J39" s="19">
         <v>1.33</v>
       </c>
-      <c r="K39" s="24" t="s">
+      <c r="K39" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
+      <c r="A42" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
     </row>
     <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2302,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2315,31 +2291,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2382,22 +2358,22 @@
         <v>35</v>
       </c>
       <c r="D3" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="9">
         <v>-6.85</v>
       </c>
       <c r="F3" s="9">
-        <v>-12.85</v>
+        <v>-10.85</v>
       </c>
       <c r="G3" s="9">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H3" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" s="8">
-        <v>12.86</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2408,25 +2384,25 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="12">
-        <v>-12.85</v>
+        <v>-10.85</v>
       </c>
       <c r="F4" s="12">
         <v>-20.85</v>
       </c>
       <c r="G4" s="12">
-        <v>8.37</v>
+        <v>3.42</v>
       </c>
       <c r="H4" s="12">
-        <v>8</v>
-      </c>
-      <c r="I4" s="15">
-        <v>0.96</v>
+        <v>10</v>
+      </c>
+      <c r="I4" s="19">
+        <v>2.93</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2437,25 +2413,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D5" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="16">
         <v>-20.85</v>
       </c>
       <c r="F5" s="16">
-        <v>-50.05</v>
+        <v>-53.05</v>
       </c>
       <c r="G5" s="16">
-        <v>4.22</v>
+        <v>4.43</v>
       </c>
       <c r="H5" s="16">
-        <v>29.2</v>
+        <v>32.2</v>
       </c>
       <c r="I5" s="8">
-        <v>6.92</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2466,83 +2442,54 @@
         <v>11</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="20">
         <v>1</v>
       </c>
       <c r="E6" s="20">
-        <v>-50.05</v>
+        <v>-53.05</v>
       </c>
       <c r="F6" s="20">
-        <v>-53.05</v>
+        <v>-55.05</v>
       </c>
       <c r="G6" s="20">
-        <v>0.37</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="20">
-        <v>3</v>
-      </c>
-      <c r="I6" s="8">
-        <v>8.18</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
-        <v>6</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="23">
-        <v>1</v>
-      </c>
-      <c r="E7" s="23">
-        <v>-53.05</v>
-      </c>
-      <c r="F7" s="23">
+        <v>2</v>
+      </c>
+      <c r="I6" s="19">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="25">
+        <v>29</v>
+      </c>
+      <c r="E7" s="25">
+        <v>3.2</v>
+      </c>
+      <c r="F7" s="25">
         <v>-55.05</v>
       </c>
-      <c r="G7" s="23">
-        <v>1.5</v>
-      </c>
-      <c r="H7" s="23">
-        <v>2</v>
-      </c>
-      <c r="I7" s="19">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="28">
-        <v>29</v>
-      </c>
-      <c r="E8" s="28">
-        <v>3.2</v>
-      </c>
-      <c r="F8" s="28">
-        <v>-55.05</v>
-      </c>
-      <c r="G8" s="28">
-        <v>15.85</v>
-      </c>
-      <c r="H8" s="28">
+      <c r="G7" s="25">
+        <v>10.7</v>
+      </c>
+      <c r="H7" s="25">
         <v>58.25</v>
       </c>
-      <c r="I8" s="28">
-        <v>3.68</v>
+      <c r="I7" s="25">
+        <v>5.44</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/994164ae-7868-4a32-8af2-201eaa43099d_Cáp_treo_-_Khu_VAP_TP-2_D1200_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/994164ae-7868-4a32-8af2-201eaa43099d_Cáp_treo_-_Khu_VAP_TP-2_D1200_14-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>1200</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/994164ae-7868-4a32-8af2-201eaa43099d_Cáp_treo_-_Khu_VAP_TP-2_D1200_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/994164ae-7868-4a32-8af2-201eaa43099d_Cáp_treo_-_Khu_VAP_TP-2_D1200_14-03-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>11:00 13/03/2025</t>
+    <t>11:00 13/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>10:15 14/03/2025</t>
+    <t>10:15 14/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,45 +99,45 @@
   </si>
   <si>
     <t xml:space="preserve">11:09
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:15
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:25
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:35
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:50
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:05
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha - Sét pha màu xám ghi, xám xanh, đôi chỗ lẫn vỏ sò, hữu cơ (gỗ, lá, rễ cây...), trạng thái dẻo mềm đến dẻo chảy</t>
+    <t>Cát pha - sét pha màu xám ghi, xám xanh, đôi khi lẫn vỏ sò, hữu cơ, trạng thái dẻo mềm đến dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">12:15
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:00
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:15
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -147,23 +147,23 @@
   </si>
   <si>
     <t xml:space="preserve">17:18
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:33
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:45
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:29
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:40
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -173,83 +173,83 @@
   </si>
   <si>
     <t xml:space="preserve">20:50
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:10
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:20
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:02
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:14
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:30
-13/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:18
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:25
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:35
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:50
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:08
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:35
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:55
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:08
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:20
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:50
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:32
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:42
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:23
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:45
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -259,7 +259,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:15
-14/03/2025</t>
+13/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
